--- a/Config/Datas/Mascots/Mascots.xlsx
+++ b/Config/Datas/Mascots/Mascots.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UnityProject\BBQ\Config\Datas\Mascots\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\Mascots\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{193733C4-60AF-4149-91F9-09307292D5CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{682C16F2-B217-462A-AE43-A5BCF67F2CC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="43">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -168,6 +168,34 @@
   </si>
   <si>
     <t>*conditions</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>牌佬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>抽牌不断</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每抽一张技能牌，随机使得一个食材+1/+1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>抽牌后</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GA_为食材加属性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DV_值,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>随机,DV_值~1,棋盘上</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -233,7 +261,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -258,6 +286,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -539,20 +570,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T9"/>
+  <dimension ref="A1:V10"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="5" max="5" width="13.75" customWidth="1"/>
     <col min="8" max="8" width="13.75" customWidth="1"/>
     <col min="9" max="9" width="14.375" customWidth="1"/>
     <col min="10" max="10" width="4.5" customWidth="1"/>
-    <col min="11" max="11" width="19.5" customWidth="1"/>
-    <col min="12" max="14" width="20.375" customWidth="1"/>
-    <col min="15" max="15" width="17.25" customWidth="1"/>
-    <col min="16" max="16" width="18.75" customWidth="1"/>
-    <col min="17" max="17" width="13.375" customWidth="1"/>
+    <col min="11" max="11" width="12.375" customWidth="1"/>
+    <col min="12" max="12" width="11.125" customWidth="1"/>
+    <col min="13" max="13" width="13.875" customWidth="1"/>
+    <col min="14" max="14" width="11.625" customWidth="1"/>
+    <col min="15" max="15" width="10.25" customWidth="1"/>
+    <col min="16" max="16" width="18.875" customWidth="1"/>
+    <col min="17" max="17" width="17.25" customWidth="1"/>
+    <col min="18" max="18" width="18.75" customWidth="1"/>
+    <col min="19" max="19" width="13.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -586,11 +622,13 @@
       <c r="O1" s="6"/>
       <c r="P1" s="6"/>
       <c r="Q1" s="6"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
+      <c r="R1" s="6"/>
+      <c r="S1" s="6"/>
       <c r="T1" s="1"/>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U1" s="1"/>
+      <c r="V1" s="1"/>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -624,11 +662,13 @@
       <c r="O2" s="6"/>
       <c r="P2" s="6"/>
       <c r="Q2" s="6"/>
-      <c r="R2" s="1"/>
-      <c r="S2" s="1"/>
+      <c r="R2" s="6"/>
+      <c r="S2" s="6"/>
       <c r="T2" s="1"/>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -653,8 +693,10 @@
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="O3" s="1"/>
+      <c r="P3" s="1"/>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -671,13 +713,15 @@
       <c r="L4" s="7"/>
       <c r="M4" s="7"/>
       <c r="N4" s="7"/>
-      <c r="O4" s="8" t="s">
+      <c r="O4" s="7"/>
+      <c r="P4" s="7"/>
+      <c r="Q4" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="P4" s="8"/>
-      <c r="Q4" s="8"/>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="R4" s="8"/>
+      <c r="S4" s="8"/>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -692,13 +736,15 @@
         <v>31</v>
       </c>
       <c r="N5" s="7"/>
-      <c r="P5" s="5"/>
-      <c r="Q5" s="5"/>
+      <c r="O5" s="7"/>
+      <c r="P5" s="7"/>
       <c r="R5" s="5"/>
       <c r="S5" s="5"/>
       <c r="T5" s="5"/>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U5" s="5"/>
+      <c r="V5" s="5"/>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6">
         <v>1</v>
       </c>
@@ -733,10 +779,10 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B8">
         <v>2</v>
       </c>
@@ -771,18 +817,59 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
     </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="B10">
+        <v>3</v>
+      </c>
+      <c r="C10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10" t="b">
+        <v>1</v>
+      </c>
+      <c r="H10" t="s">
+        <v>21</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="J10" s="9">
+        <v>1</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="N10" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="O10" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="P10" s="9" t="s">
+        <v>42</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="H1:Q1"/>
+    <mergeCell ref="H1:S1"/>
     <mergeCell ref="K5:L5"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="J4:N4"/>
-    <mergeCell ref="O4:Q4"/>
-    <mergeCell ref="H2:Q2"/>
+    <mergeCell ref="Q4:S4"/>
+    <mergeCell ref="H2:S2"/>
+    <mergeCell ref="M5:P5"/>
+    <mergeCell ref="J4:P4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/Datas/Mascots/Mascots.xlsx
+++ b/Config/Datas/Mascots/Mascots.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\Mascots\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{682C16F2-B217-462A-AE43-A5BCF67F2CC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35630AC4-E720-4A7A-ACC3-8488B01015C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="50">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -196,6 +196,34 @@
   </si>
   <si>
     <t>随机,DV_值~1,棋盘上</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>美味</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>珍稀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GA_直接修改当前烧烤值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DV_值,8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DV_值,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DV_值,40</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>串串构建时</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -570,7 +598,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V10"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="5" max="5" width="13.75" customWidth="1"/>
@@ -579,7 +607,7 @@
     <col min="10" max="10" width="4.5" customWidth="1"/>
     <col min="11" max="11" width="12.375" customWidth="1"/>
     <col min="12" max="12" width="11.125" customWidth="1"/>
-    <col min="13" max="13" width="13.875" customWidth="1"/>
+    <col min="13" max="13" width="21" customWidth="1"/>
     <col min="14" max="14" width="11.625" customWidth="1"/>
     <col min="15" max="15" width="10.25" customWidth="1"/>
     <col min="16" max="16" width="18.875" customWidth="1"/>
@@ -862,6 +890,70 @@
         <v>42</v>
       </c>
     </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="B12">
+        <v>4</v>
+      </c>
+      <c r="C12" t="s">
+        <v>43</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H12" t="s">
+        <v>21</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="J12" s="9">
+        <v>1</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="N12" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="O12" s="9" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="B13">
+        <v>5</v>
+      </c>
+      <c r="C13" t="s">
+        <v>44</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13" t="b">
+        <v>1</v>
+      </c>
+      <c r="H13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="J13" s="9">
+        <v>1</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="N13" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="O13" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="H1:S1"/>

--- a/Config/Datas/Mascots/Mascots.xlsx
+++ b/Config/Datas/Mascots/Mascots.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\Mascots\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35630AC4-E720-4A7A-ACC3-8488B01015C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F9FB31E-3546-4660-A3D0-5CF8D6D91196}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="53">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -224,6 +224,18 @@
   </si>
   <si>
     <t>串串构建时</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小而精</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DV_当前串空位数,* 2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>烤串构建完成时，为该串增加 2*空位数 的珍稀度</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -306,6 +318,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -314,9 +329,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -598,25 +610,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V13"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:V15"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="5" max="5" width="13.75" customWidth="1"/>
     <col min="8" max="8" width="13.75" customWidth="1"/>
-    <col min="9" max="9" width="14.375" customWidth="1"/>
+    <col min="9" max="9" width="14.33203125" customWidth="1"/>
     <col min="10" max="10" width="4.5" customWidth="1"/>
-    <col min="11" max="11" width="12.375" customWidth="1"/>
-    <col min="12" max="12" width="11.125" customWidth="1"/>
+    <col min="11" max="11" width="12.33203125" customWidth="1"/>
+    <col min="12" max="12" width="11.08203125" customWidth="1"/>
     <col min="13" max="13" width="21" customWidth="1"/>
-    <col min="14" max="14" width="11.625" customWidth="1"/>
+    <col min="14" max="14" width="11.58203125" customWidth="1"/>
     <col min="15" max="15" width="10.25" customWidth="1"/>
-    <col min="16" max="16" width="18.875" customWidth="1"/>
+    <col min="16" max="16" width="18.83203125" customWidth="1"/>
     <col min="17" max="17" width="17.25" customWidth="1"/>
     <col min="18" max="18" width="18.75" customWidth="1"/>
-    <col min="19" max="19" width="13.375" customWidth="1"/>
+    <col min="19" max="19" width="13.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -638,25 +650,25 @@
       <c r="G1" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
+      <c r="M1" s="7"/>
+      <c r="N1" s="7"/>
+      <c r="O1" s="7"/>
+      <c r="P1" s="7"/>
+      <c r="Q1" s="7"/>
+      <c r="R1" s="7"/>
+      <c r="S1" s="7"/>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -678,25 +690,25 @@
       <c r="G2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="6"/>
-      <c r="R2" s="6"/>
-      <c r="S2" s="6"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="7"/>
+      <c r="O2" s="7"/>
+      <c r="P2" s="7"/>
+      <c r="Q2" s="7"/>
+      <c r="R2" s="7"/>
+      <c r="S2" s="7"/>
       <c r="T2" s="1"/>
       <c r="U2" s="1"/>
       <c r="V2" s="1"/>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -724,7 +736,7 @@
       <c r="O3" s="1"/>
       <c r="P3" s="1"/>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -734,45 +746,45 @@
       <c r="I4" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="J4" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
-      <c r="M4" s="7"/>
-      <c r="N4" s="7"/>
-      <c r="O4" s="7"/>
-      <c r="P4" s="7"/>
-      <c r="Q4" s="8" t="s">
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="8"/>
+      <c r="N4" s="8"/>
+      <c r="O4" s="8"/>
+      <c r="P4" s="8"/>
+      <c r="Q4" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="R4" s="8"/>
-      <c r="S4" s="8"/>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="R4" s="9"/>
+      <c r="S4" s="9"/>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>0</v>
       </c>
       <c r="J5" t="s">
         <v>1</v>
       </c>
-      <c r="K5" s="7" t="s">
+      <c r="K5" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="L5" s="7"/>
-      <c r="M5" s="7" t="s">
+      <c r="L5" s="8"/>
+      <c r="M5" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="N5" s="7"/>
-      <c r="O5" s="7"/>
-      <c r="P5" s="7"/>
+      <c r="N5" s="8"/>
+      <c r="O5" s="8"/>
+      <c r="P5" s="8"/>
       <c r="R5" s="5"/>
       <c r="S5" s="5"/>
       <c r="T5" s="5"/>
       <c r="U5" s="5"/>
       <c r="V5" s="5"/>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B6">
         <v>1</v>
       </c>
@@ -807,10 +819,10 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="R7" s="2"/>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B8">
         <v>2</v>
       </c>
@@ -845,11 +857,11 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B10">
         <v>3</v>
       </c>
@@ -874,23 +886,23 @@
       <c r="I10" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="J10" s="9">
+      <c r="J10" s="6">
         <v>1</v>
       </c>
       <c r="M10" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="N10" s="9" t="s">
+      <c r="N10" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="O10" s="9" t="s">
+      <c r="O10" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="P10" s="9" t="s">
+      <c r="P10" s="6" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B12">
         <v>4</v>
       </c>
@@ -909,20 +921,20 @@
       <c r="I12" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="J12" s="9">
+      <c r="J12" s="6">
         <v>1</v>
       </c>
       <c r="M12" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="N12" s="9" t="s">
+      <c r="N12" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="O12" s="9" t="s">
+      <c r="O12" s="6" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B13">
         <v>5</v>
       </c>
@@ -941,16 +953,51 @@
       <c r="I13" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="J13" s="9">
+      <c r="J13" s="6">
         <v>1</v>
       </c>
       <c r="M13" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="N13" s="9" t="s">
+      <c r="N13" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="O13" s="9" t="s">
+      <c r="O13" s="6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B15">
+        <v>6</v>
+      </c>
+      <c r="C15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E15" t="s">
+        <v>52</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15" t="b">
+        <v>0</v>
+      </c>
+      <c r="H15" t="s">
+        <v>21</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="J15" s="6">
+        <v>1</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="O15" s="6" t="s">
         <v>47</v>
       </c>
     </row>
